--- a/Extracted_data_analysis/temperate/Output-Transformed_data/summary_counts_question_4.xlsx
+++ b/Extracted_data_analysis/temperate/Output-Transformed_data/summary_counts_question_4.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="189" uniqueCount="189">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="191" uniqueCount="191">
   <si>
     <t xml:space="preserve">meso_design</t>
   </si>
@@ -243,6 +243,9 @@
     <t xml:space="preserve">site(sample)+site(transect)</t>
   </si>
   <si>
+    <t xml:space="preserve">site(specimen)</t>
+  </si>
+  <si>
     <t xml:space="preserve">site(stationary)</t>
   </si>
   <si>
@@ -517,6 +520,9 @@
   </si>
   <si>
     <t xml:space="preserve">ph+salinity+temperature</t>
+  </si>
+  <si>
+    <t xml:space="preserve">poc+pom</t>
   </si>
   <si>
     <t xml:space="preserve">pollutant</t>
@@ -1117,7 +1123,7 @@
         <v>42</v>
       </c>
       <c r="C19" t="n">
-        <v>8.1</v>
+        <v>8</v>
       </c>
     </row>
     <row r="20">
@@ -1194,7 +1200,7 @@
         <v>6</v>
       </c>
       <c r="C26" t="n">
-        <v>1.2</v>
+        <v>1.1</v>
       </c>
     </row>
     <row r="27">
@@ -1469,7 +1475,7 @@
         <v>55</v>
       </c>
       <c r="C51" t="n">
-        <v>10.6</v>
+        <v>10.5</v>
       </c>
     </row>
     <row r="52">
@@ -1686,10 +1692,10 @@
         <v>72</v>
       </c>
       <c r="B71" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="C71" t="n">
-        <v>2.3</v>
+        <v>2.5</v>
       </c>
     </row>
     <row r="72">
@@ -1730,10 +1736,10 @@
         <v>76</v>
       </c>
       <c r="B75" t="n">
-        <v>20</v>
+        <v>1</v>
       </c>
       <c r="C75" t="n">
-        <v>3.8</v>
+        <v>0.2</v>
       </c>
     </row>
     <row r="76">
@@ -1741,10 +1747,10 @@
         <v>77</v>
       </c>
       <c r="B76" t="n">
-        <v>2</v>
+        <v>20</v>
       </c>
       <c r="C76" t="n">
-        <v>0.4</v>
+        <v>3.8</v>
       </c>
     </row>
     <row r="77">
@@ -1752,10 +1758,10 @@
         <v>78</v>
       </c>
       <c r="B77" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C77" t="n">
-        <v>0.2</v>
+        <v>0.4</v>
       </c>
     </row>
     <row r="78">
@@ -1763,10 +1769,10 @@
         <v>79</v>
       </c>
       <c r="B78" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C78" t="n">
-        <v>0.4</v>
+        <v>0.2</v>
       </c>
     </row>
     <row r="79">
@@ -1774,10 +1780,10 @@
         <v>80</v>
       </c>
       <c r="B79" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C79" t="n">
-        <v>0.2</v>
+        <v>0.4</v>
       </c>
     </row>
     <row r="80">
@@ -1785,10 +1791,10 @@
         <v>81</v>
       </c>
       <c r="B80" t="n">
-        <v>45</v>
+        <v>1</v>
       </c>
       <c r="C80" t="n">
-        <v>8.7</v>
+        <v>0.2</v>
       </c>
     </row>
     <row r="81">
@@ -1796,10 +1802,10 @@
         <v>82</v>
       </c>
       <c r="B81" t="n">
-        <v>1</v>
+        <v>45</v>
       </c>
       <c r="C81" t="n">
-        <v>0.2</v>
+        <v>8.6</v>
       </c>
     </row>
     <row r="82">
@@ -1829,10 +1835,10 @@
         <v>85</v>
       </c>
       <c r="B84" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C84" t="n">
-        <v>0.4</v>
+        <v>0.2</v>
       </c>
     </row>
     <row r="85">
@@ -1840,10 +1846,10 @@
         <v>86</v>
       </c>
       <c r="B85" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C85" t="n">
-        <v>0.2</v>
+        <v>0.4</v>
       </c>
     </row>
     <row r="86">
@@ -1851,10 +1857,10 @@
         <v>87</v>
       </c>
       <c r="B86" t="n">
-        <v>34</v>
+        <v>1</v>
       </c>
       <c r="C86" t="n">
-        <v>6.5</v>
+        <v>0.2</v>
       </c>
     </row>
     <row r="87">
@@ -1862,10 +1868,10 @@
         <v>88</v>
       </c>
       <c r="B87" t="n">
-        <v>1</v>
+        <v>34</v>
       </c>
       <c r="C87" t="n">
-        <v>0.2</v>
+        <v>6.5</v>
       </c>
     </row>
     <row r="88">
@@ -1906,10 +1912,10 @@
         <v>92</v>
       </c>
       <c r="B91" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C91" t="n">
-        <v>0.4</v>
+        <v>0.2</v>
       </c>
     </row>
     <row r="92">
@@ -1917,10 +1923,10 @@
         <v>93</v>
       </c>
       <c r="B92" t="n">
-        <v>41</v>
+        <v>2</v>
       </c>
       <c r="C92" t="n">
-        <v>7.9</v>
+        <v>0.4</v>
       </c>
     </row>
     <row r="93">
@@ -1928,10 +1934,10 @@
         <v>94</v>
       </c>
       <c r="B93" t="n">
-        <v>7</v>
+        <v>41</v>
       </c>
       <c r="C93" t="n">
-        <v>1.3</v>
+        <v>7.9</v>
       </c>
     </row>
     <row r="94">
@@ -1939,10 +1945,10 @@
         <v>95</v>
       </c>
       <c r="B94" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="C94" t="n">
-        <v>0.2</v>
+        <v>1.3</v>
       </c>
     </row>
     <row r="95">
@@ -1961,10 +1967,10 @@
         <v>97</v>
       </c>
       <c r="B96" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C96" t="n">
-        <v>0.4</v>
+        <v>0.2</v>
       </c>
     </row>
     <row r="97">
@@ -1972,10 +1978,10 @@
         <v>98</v>
       </c>
       <c r="B97" t="n">
-        <v>9</v>
+        <v>2</v>
       </c>
       <c r="C97" t="n">
-        <v>1.7</v>
+        <v>0.4</v>
       </c>
     </row>
     <row r="98">
@@ -1983,10 +1989,10 @@
         <v>99</v>
       </c>
       <c r="B98" t="n">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="C98" t="n">
-        <v>0.2</v>
+        <v>1.7</v>
       </c>
     </row>
     <row r="99">
@@ -1994,10 +2000,10 @@
         <v>100</v>
       </c>
       <c r="B99" t="n">
-        <v>9</v>
+        <v>1</v>
       </c>
       <c r="C99" t="n">
-        <v>1.7</v>
+        <v>0.2</v>
       </c>
     </row>
     <row r="100">
@@ -2005,9 +2011,20 @@
         <v>101</v>
       </c>
       <c r="B100" t="n">
+        <v>9</v>
+      </c>
+      <c r="C100" t="n">
+        <v>1.7</v>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" t="s">
+        <v>102</v>
+      </c>
+      <c r="B101" t="n">
         <v>2</v>
       </c>
-      <c r="C100" t="n">
+      <c r="C101" t="n">
         <v>0.4</v>
       </c>
     </row>
@@ -2024,7 +2041,7 @@
   <sheetData>
     <row r="1">
       <c r="A1" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="B1" t="s">
         <v>1</v>
@@ -2046,7 +2063,7 @@
     </row>
     <row r="3">
       <c r="A3" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="B3" t="n">
         <v>17</v>
@@ -2057,13 +2074,13 @@
     </row>
     <row r="4">
       <c r="A4" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="B4" t="n">
-        <v>489</v>
+        <v>491</v>
       </c>
       <c r="C4" t="n">
-        <v>93.1</v>
+        <v>93.2</v>
       </c>
     </row>
   </sheetData>
@@ -2079,7 +2096,7 @@
   <sheetData>
     <row r="1">
       <c r="A1" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="B1" t="s">
         <v>1</v>
@@ -2101,24 +2118,24 @@
     </row>
     <row r="3">
       <c r="A3" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="B3" t="n">
-        <v>386</v>
+        <v>387</v>
       </c>
       <c r="C3" t="n">
-        <v>73.5</v>
+        <v>73.4</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="B4" t="n">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="C4" t="n">
-        <v>25.7</v>
+        <v>25.8</v>
       </c>
     </row>
   </sheetData>
@@ -2134,7 +2151,7 @@
   <sheetData>
     <row r="1">
       <c r="A1" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="B1" t="s">
         <v>1</v>
@@ -2145,18 +2162,18 @@
     </row>
     <row r="2">
       <c r="A2" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="B2" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="C2" t="n">
-        <v>4</v>
+        <v>4.1</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="B3" t="n">
         <v>23</v>
@@ -2167,13 +2184,13 @@
     </row>
     <row r="4">
       <c r="A4" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="B4" t="n">
-        <v>174</v>
+        <v>176</v>
       </c>
       <c r="C4" t="n">
-        <v>32.9</v>
+        <v>33.1</v>
       </c>
     </row>
     <row r="5">
@@ -2189,13 +2206,13 @@
     </row>
     <row r="6">
       <c r="A6" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="B6" t="n">
         <v>310</v>
       </c>
       <c r="C6" t="n">
-        <v>58.6</v>
+        <v>58.3</v>
       </c>
     </row>
   </sheetData>
@@ -2211,7 +2228,7 @@
   <sheetData>
     <row r="1">
       <c r="A1" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="B1" t="s">
         <v>1</v>
@@ -2222,7 +2239,7 @@
     </row>
     <row r="2">
       <c r="A2" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="B2" t="n">
         <v>1</v>
@@ -2233,7 +2250,7 @@
     </row>
     <row r="3">
       <c r="A3" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="B3" t="n">
         <v>1</v>
@@ -2244,7 +2261,7 @@
     </row>
     <row r="4">
       <c r="A4" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="B4" t="n">
         <v>1</v>
@@ -2255,7 +2272,7 @@
     </row>
     <row r="5">
       <c r="A5" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="B5" t="n">
         <v>1</v>
@@ -2266,7 +2283,7 @@
     </row>
     <row r="6">
       <c r="A6" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="B6" t="n">
         <v>1</v>
@@ -2277,7 +2294,7 @@
     </row>
     <row r="7">
       <c r="A7" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="B7" t="n">
         <v>1</v>
@@ -2288,7 +2305,7 @@
     </row>
     <row r="8">
       <c r="A8" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="B8" t="n">
         <v>1</v>
@@ -2299,7 +2316,7 @@
     </row>
     <row r="9">
       <c r="A9" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="B9" t="n">
         <v>1</v>
@@ -2310,7 +2327,7 @@
     </row>
     <row r="10">
       <c r="A10" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="B10" t="n">
         <v>1</v>
@@ -2321,7 +2338,7 @@
     </row>
     <row r="11">
       <c r="A11" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="B11" t="n">
         <v>1</v>
@@ -2332,7 +2349,7 @@
     </row>
     <row r="12">
       <c r="A12" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="B12" t="n">
         <v>1</v>
@@ -2343,7 +2360,7 @@
     </row>
     <row r="13">
       <c r="A13" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="B13" t="n">
         <v>3</v>
@@ -2354,7 +2371,7 @@
     </row>
     <row r="14">
       <c r="A14" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="B14" t="n">
         <v>3</v>
@@ -2365,7 +2382,7 @@
     </row>
     <row r="15">
       <c r="A15" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="B15" t="n">
         <v>1</v>
@@ -2376,7 +2393,7 @@
     </row>
     <row r="16">
       <c r="A16" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="B16" t="n">
         <v>1</v>
@@ -2387,7 +2404,7 @@
     </row>
     <row r="17">
       <c r="A17" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="B17" t="n">
         <v>1</v>
@@ -2398,7 +2415,7 @@
     </row>
     <row r="18">
       <c r="A18" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="B18" t="n">
         <v>1</v>
@@ -2409,7 +2426,7 @@
     </row>
     <row r="19">
       <c r="A19" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="B19" t="n">
         <v>1</v>
@@ -2420,7 +2437,7 @@
     </row>
     <row r="20">
       <c r="A20" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="B20" t="n">
         <v>1</v>
@@ -2431,7 +2448,7 @@
     </row>
     <row r="21">
       <c r="A21" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="B21" t="n">
         <v>1</v>
@@ -2442,7 +2459,7 @@
     </row>
     <row r="22">
       <c r="A22" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="B22" t="n">
         <v>1</v>
@@ -2453,7 +2470,7 @@
     </row>
     <row r="23">
       <c r="A23" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="B23" t="n">
         <v>1</v>
@@ -2464,18 +2481,18 @@
     </row>
     <row r="24">
       <c r="A24" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="B24" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C24" t="n">
-        <v>0.4</v>
+        <v>0.6</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="B25" t="n">
         <v>2</v>
@@ -2486,7 +2503,7 @@
     </row>
     <row r="26">
       <c r="A26" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="B26" t="n">
         <v>2</v>
@@ -2497,7 +2514,7 @@
     </row>
     <row r="27">
       <c r="A27" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="B27" t="n">
         <v>1</v>
@@ -2508,7 +2525,7 @@
     </row>
     <row r="28">
       <c r="A28" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="B28" t="n">
         <v>1</v>
@@ -2519,7 +2536,7 @@
     </row>
     <row r="29">
       <c r="A29" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="B29" t="n">
         <v>1</v>
@@ -2530,7 +2547,7 @@
     </row>
     <row r="30">
       <c r="A30" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="B30" t="n">
         <v>1</v>
@@ -2541,7 +2558,7 @@
     </row>
     <row r="31">
       <c r="A31" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="B31" t="n">
         <v>1</v>
@@ -2552,7 +2569,7 @@
     </row>
     <row r="32">
       <c r="A32" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="B32" t="n">
         <v>1</v>
@@ -2563,7 +2580,7 @@
     </row>
     <row r="33">
       <c r="A33" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="B33" t="n">
         <v>2</v>
@@ -2574,7 +2591,7 @@
     </row>
     <row r="34">
       <c r="A34" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="B34" t="n">
         <v>1</v>
@@ -2585,7 +2602,7 @@
     </row>
     <row r="35">
       <c r="A35" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="B35" t="n">
         <v>1</v>
@@ -2596,7 +2613,7 @@
     </row>
     <row r="36">
       <c r="A36" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="B36" t="n">
         <v>1</v>
@@ -2607,7 +2624,7 @@
     </row>
     <row r="37">
       <c r="A37" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="B37" t="n">
         <v>1</v>
@@ -2618,7 +2635,7 @@
     </row>
     <row r="38">
       <c r="A38" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="B38" t="n">
         <v>1</v>
@@ -2629,7 +2646,7 @@
     </row>
     <row r="39">
       <c r="A39" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="B39" t="n">
         <v>1</v>
@@ -2640,7 +2657,7 @@
     </row>
     <row r="40">
       <c r="A40" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="B40" t="n">
         <v>1</v>
@@ -2651,7 +2668,7 @@
     </row>
     <row r="41">
       <c r="A41" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="B41" t="n">
         <v>1</v>
@@ -2662,7 +2679,7 @@
     </row>
     <row r="42">
       <c r="A42" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="B42" t="n">
         <v>1</v>
@@ -2695,18 +2712,18 @@
     </row>
     <row r="45">
       <c r="A45" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="B45" t="n">
         <v>308</v>
       </c>
       <c r="C45" t="n">
-        <v>58.1</v>
+        <v>57.9</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="B46" t="n">
         <v>1</v>
@@ -2717,7 +2734,7 @@
     </row>
     <row r="47">
       <c r="A47" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="B47" t="n">
         <v>1</v>
@@ -2728,7 +2745,7 @@
     </row>
     <row r="48">
       <c r="A48" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="B48" t="n">
         <v>1</v>
@@ -2739,7 +2756,7 @@
     </row>
     <row r="49">
       <c r="A49" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="B49" t="n">
         <v>1</v>
@@ -2750,7 +2767,7 @@
     </row>
     <row r="50">
       <c r="A50" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="B50" t="n">
         <v>2</v>
@@ -2761,7 +2778,7 @@
     </row>
     <row r="51">
       <c r="A51" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="B51" t="n">
         <v>1</v>
@@ -2772,7 +2789,7 @@
     </row>
     <row r="52">
       <c r="A52" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="B52" t="n">
         <v>1</v>
@@ -2783,7 +2800,7 @@
     </row>
     <row r="53">
       <c r="A53" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="B53" t="n">
         <v>1</v>
@@ -2794,7 +2811,7 @@
     </row>
     <row r="54">
       <c r="A54" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="B54" t="n">
         <v>1</v>
@@ -2805,7 +2822,7 @@
     </row>
     <row r="55">
       <c r="A55" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="B55" t="n">
         <v>2</v>
@@ -2816,7 +2833,7 @@
     </row>
     <row r="56">
       <c r="A56" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="B56" t="n">
         <v>1</v>
@@ -2827,7 +2844,7 @@
     </row>
     <row r="57">
       <c r="A57" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="B57" t="n">
         <v>1</v>
@@ -2838,7 +2855,7 @@
     </row>
     <row r="58">
       <c r="A58" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="B58" t="n">
         <v>2</v>
@@ -2849,7 +2866,7 @@
     </row>
     <row r="59">
       <c r="A59" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="B59" t="n">
         <v>1</v>
@@ -2860,7 +2877,7 @@
     </row>
     <row r="60">
       <c r="A60" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="B60" t="n">
         <v>1</v>
@@ -2871,7 +2888,7 @@
     </row>
     <row r="61">
       <c r="A61" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="B61" t="n">
         <v>1</v>
@@ -2882,7 +2899,7 @@
     </row>
     <row r="62">
       <c r="A62" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="B62" t="n">
         <v>1</v>
@@ -2893,62 +2910,62 @@
     </row>
     <row r="63">
       <c r="A63" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="B63" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C63" t="n">
-        <v>0.4</v>
+        <v>0.2</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="B64" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C64" t="n">
-        <v>0.2</v>
+        <v>0.4</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="B65" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C65" t="n">
-        <v>0.6</v>
+        <v>0.2</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="B66" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C66" t="n">
-        <v>0.2</v>
+        <v>0.6</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="B67" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C67" t="n">
-        <v>0.4</v>
+        <v>0.2</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="B68" t="n">
         <v>2</v>
@@ -2959,62 +2976,62 @@
     </row>
     <row r="69">
       <c r="A69" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="B69" t="n">
-        <v>10</v>
+        <v>2</v>
       </c>
       <c r="C69" t="n">
-        <v>1.9</v>
+        <v>0.4</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="B70" t="n">
-        <v>39</v>
+        <v>10</v>
       </c>
       <c r="C70" t="n">
-        <v>7.4</v>
+        <v>1.9</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="B71" t="n">
-        <v>7</v>
+        <v>39</v>
       </c>
       <c r="C71" t="n">
-        <v>1.3</v>
+        <v>7.3</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="B72" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="C72" t="n">
-        <v>0.6</v>
+        <v>1.3</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="B73" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C73" t="n">
-        <v>0.2</v>
+        <v>0.6</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="B74" t="n">
         <v>1</v>
@@ -3025,51 +3042,51 @@
     </row>
     <row r="75">
       <c r="A75" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="B75" t="n">
-        <v>44</v>
+        <v>1</v>
       </c>
       <c r="C75" t="n">
-        <v>8.3</v>
+        <v>0.2</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="B76" t="n">
-        <v>3</v>
+        <v>44</v>
       </c>
       <c r="C76" t="n">
-        <v>0.6</v>
+        <v>8.3</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="B77" t="n">
-        <v>24</v>
+        <v>3</v>
       </c>
       <c r="C77" t="n">
-        <v>4.5</v>
+        <v>0.6</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="B78" t="n">
-        <v>1</v>
+        <v>24</v>
       </c>
       <c r="C78" t="n">
-        <v>0.2</v>
+        <v>4.5</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="B79" t="n">
         <v>1</v>
@@ -3080,34 +3097,45 @@
     </row>
     <row r="80">
       <c r="A80" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="B80" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C80" t="n">
-        <v>0.6</v>
+        <v>0.2</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="B81" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C81" t="n">
-        <v>0.2</v>
+        <v>0.6</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="B82" t="n">
         <v>1</v>
       </c>
       <c r="C82" t="n">
+        <v>0.2</v>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" t="s">
+        <v>190</v>
+      </c>
+      <c r="B83" t="n">
+        <v>1</v>
+      </c>
+      <c r="C83" t="n">
         <v>0.2</v>
       </c>
     </row>
